--- a/journal_analyzer/graphy/감사조서/graphy_mapping_list_26년.xlsx
+++ b/journal_analyzer/graphy/감사조서/graphy_mapping_list_26년.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>데이터개요_요약</t>
+          <t>요약</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>은행조회서완전성</t>
+          <t>전체내역</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>금융기관_조회서목록</t>
+          <t>금융기관별목록</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>벤포드_외상매출금_차변</t>
+          <t>외상매출금_차</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>벤포드_외상매출금_차변</t>
+          <t>외상매출금_차</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>상대_외상매출금_차변</t>
+          <t>외상매출금_차</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>벤포드_외상매입금_대변</t>
+          <t>외상매입금_대</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>벤포드_외상매입금_대변</t>
+          <t>외상매입금_대</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>상대_외상매입금_대변</t>
+          <t>외상매입금_대</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>손익월별_매출</t>
+          <t>매출</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>비교_해외제품매출액</t>
+          <t>해외제품매출액</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>비교_해외상품매출액</t>
+          <t>해외상품매출액</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>비교_국내제품매출액</t>
+          <t>국내제품매출액</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>비교_국내상품매출액</t>
+          <t>국내상품매출액</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>매출비용교차</t>
+          <t>매출 vs 비용 교차</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>벤포드_국내제품매출액_대변</t>
+          <t>국내제품매출액_대</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>벤포드_국내제품매출액_대변</t>
+          <t>국내제품매출액_대</t>
         </is>
       </c>
       <c r="D20" s="8" t="n"/>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>벤포드_해외제품매출액_대변</t>
+          <t>해외제품매출액_대</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>벤포드_해외제품매출액_대변</t>
+          <t>해외제품매출액_대</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>상대_국내제품매출액_대변</t>
+          <t>국내제품매출액_대</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>상대_해외제품매출액_대변</t>
+          <t>해외제품매출액_대</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>상대_국내상품매출액_대변</t>
+          <t>국내상품매출액_대</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>상대_해외상품매출액_대변</t>
+          <t>해외상품매출액_대</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
